--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ142"/>
+  <dimension ref="A1:AZ143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4995,58 +4995,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123563043</v>
+        <v>136991757</v>
       </c>
       <c r="B38" t="n">
-        <v>58636</v>
+        <v>58169</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103044</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Banvall smedsbo, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524035</v>
+        <v>524075</v>
       </c>
       <c r="R38" t="n">
-        <v>6713295</v>
+        <v>6713944</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5070,22 +5065,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5111,13 +5106,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123563043</t>
+          <t>https://artportalen.se/Sighting/136991757</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123568031</v>
+        <v>123563043</v>
       </c>
       <c r="B39" t="n">
         <v>58636</v>
@@ -5146,6 +5141,11 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -5157,13 +5157,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524094</v>
+        <v>524035</v>
       </c>
       <c r="R39" t="n">
-        <v>6713439</v>
+        <v>6713295</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5228,16 +5228,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123568031</t>
+          <t>https://artportalen.se/Sighting/123563043</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122915863</v>
+        <v>123568031</v>
       </c>
       <c r="B40" t="n">
-        <v>8455</v>
+        <v>58636</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5245,39 +5245,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>103044</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524025</v>
+        <v>524094</v>
       </c>
       <c r="R40" t="n">
-        <v>6713544</v>
+        <v>6713439</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5304,22 +5304,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5345,13 +5345,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122915863</t>
+          <t>https://artportalen.se/Sighting/123568031</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122959354</v>
+        <v>122915863</v>
       </c>
       <c r="B41" t="n">
         <v>8455</v>
@@ -5387,14 +5387,14 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524122</v>
+        <v>524025</v>
       </c>
       <c r="R41" t="n">
-        <v>6713710</v>
+        <v>6713544</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5421,22 +5421,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5462,13 +5462,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122959354</t>
+          <t>https://artportalen.se/Sighting/122915863</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122959453</v>
+        <v>122959354</v>
       </c>
       <c r="B42" t="n">
         <v>8455</v>
@@ -5508,10 +5508,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524128</v>
+        <v>524122</v>
       </c>
       <c r="R42" t="n">
-        <v>6713669</v>
+        <v>6713710</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5543,7 +5543,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5579,13 +5579,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122959453</t>
+          <t>https://artportalen.se/Sighting/122959354</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123761045</v>
+        <v>122959453</v>
       </c>
       <c r="B43" t="n">
         <v>8455</v>
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>523984</v>
+        <v>524128</v>
       </c>
       <c r="R43" t="n">
-        <v>6713796</v>
+        <v>6713669</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5655,22 +5655,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5696,13 +5696,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123761045</t>
+          <t>https://artportalen.se/Sighting/122959453</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124434324</v>
+        <v>123761045</v>
       </c>
       <c r="B44" t="n">
         <v>8455</v>
@@ -5738,14 +5738,14 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524045</v>
+        <v>523984</v>
       </c>
       <c r="R44" t="n">
-        <v>6713403</v>
+        <v>6713796</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5772,22 +5772,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5813,59 +5813,44 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124434324</t>
+          <t>https://artportalen.se/Sighting/123761045</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118592128</v>
+        <v>124434324</v>
       </c>
       <c r="B45" t="n">
-        <v>99118</v>
+        <v>8455</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5874,13 +5859,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524061</v>
+        <v>524045</v>
       </c>
       <c r="R45" t="n">
-        <v>6713302</v>
+        <v>6713403</v>
       </c>
       <c r="S45" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5904,27 +5889,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:57</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Några i blom och minst 20-30 rosetter, kanske fler.</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5933,7 +5913,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5951,13 +5930,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118592128</t>
+          <t>https://artportalen.se/Sighting/124434324</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118680065</v>
+        <v>118592128</v>
       </c>
       <c r="B46" t="n">
         <v>99118</v>
@@ -5987,14 +5966,20 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6002,14 +5987,14 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>524085</v>
+        <v>524061</v>
       </c>
       <c r="R46" t="n">
-        <v>6714124</v>
+        <v>6713302</v>
       </c>
       <c r="S46" t="n">
         <v>50</v>
@@ -6036,27 +6021,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Under mindre gran intill större tall, i blom och minst 20 rosetter.</t>
+          <t>Några i blom och minst 20-30 rosetter, kanske fler.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6065,6 +6050,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6082,13 +6068,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118680065</t>
+          <t>https://artportalen.se/Sighting/118592128</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118680241</v>
+        <v>118680065</v>
       </c>
       <c r="B47" t="n">
         <v>99118</v>
@@ -6118,7 +6104,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6126,11 +6112,6 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6142,10 +6123,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>524096</v>
+        <v>524085</v>
       </c>
       <c r="R47" t="n">
-        <v>6714118</v>
+        <v>6714124</v>
       </c>
       <c r="S47" t="n">
         <v>50</v>
@@ -6177,7 +6158,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6187,12 +6168,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Några i blom.</t>
+          <t>Under mindre gran intill större tall, i blom och minst 20 rosetter.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6218,13 +6199,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118680241</t>
+          <t>https://artportalen.se/Sighting/118680065</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118680271</v>
+        <v>118680241</v>
       </c>
       <c r="B48" t="n">
         <v>99118</v>
@@ -6254,12 +6235,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -6278,10 +6259,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>524098</v>
+        <v>524096</v>
       </c>
       <c r="R48" t="n">
-        <v>6714108</v>
+        <v>6714118</v>
       </c>
       <c r="S48" t="n">
         <v>50</v>
@@ -6328,7 +6309,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ca 10 rosetter några i blom</t>
+          <t>Några i blom.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6354,13 +6335,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118680271</t>
+          <t>https://artportalen.se/Sighting/118680241</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118680340</v>
+        <v>118680271</v>
       </c>
       <c r="B49" t="n">
         <v>99118</v>
@@ -6395,7 +6376,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -6414,10 +6395,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>524081</v>
+        <v>524098</v>
       </c>
       <c r="R49" t="n">
-        <v>6714116</v>
+        <v>6714108</v>
       </c>
       <c r="S49" t="n">
         <v>50</v>
@@ -6449,7 +6430,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6459,12 +6440,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Mycket i blom och rosetter.</t>
+          <t>Ca 10 rosetter några i blom</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6490,13 +6471,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118680340</t>
+          <t>https://artportalen.se/Sighting/118680271</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118680431</v>
+        <v>118680340</v>
       </c>
       <c r="B50" t="n">
         <v>99118</v>
@@ -6526,12 +6507,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -6550,10 +6531,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>524105</v>
+        <v>524081</v>
       </c>
       <c r="R50" t="n">
-        <v>6714054</v>
+        <v>6714116</v>
       </c>
       <c r="S50" t="n">
         <v>50</v>
@@ -6585,7 +6566,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6595,7 +6576,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Mycket i blom och rosetter.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6621,13 +6607,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118680431</t>
+          <t>https://artportalen.se/Sighting/118680340</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118680590</v>
+        <v>118680431</v>
       </c>
       <c r="B51" t="n">
         <v>99118</v>
@@ -6657,7 +6643,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6681,10 +6667,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>524083</v>
+        <v>524105</v>
       </c>
       <c r="R51" t="n">
-        <v>6714083</v>
+        <v>6714054</v>
       </c>
       <c r="S51" t="n">
         <v>50</v>
@@ -6716,7 +6702,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6726,7 +6712,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6752,13 +6738,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118680590</t>
+          <t>https://artportalen.se/Sighting/118680431</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118680966</v>
+        <v>118680590</v>
       </c>
       <c r="B52" t="n">
         <v>99118</v>
@@ -6788,12 +6774,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -6812,10 +6798,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>524064</v>
+        <v>524083</v>
       </c>
       <c r="R52" t="n">
-        <v>6714092</v>
+        <v>6714083</v>
       </c>
       <c r="S52" t="n">
         <v>50</v>
@@ -6847,7 +6833,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6857,12 +6843,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:03</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>I blom och fler rosetter på fler fläckar.</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6888,13 +6869,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118680966</t>
+          <t>https://artportalen.se/Sighting/118680590</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122817980</v>
+        <v>118680966</v>
       </c>
       <c r="B53" t="n">
         <v>99118</v>
@@ -6929,12 +6910,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6944,17 +6925,17 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>524038</v>
+        <v>524064</v>
       </c>
       <c r="R53" t="n">
-        <v>6713288</v>
+        <v>6714092</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6978,27 +6959,27 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-03-01</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>10-15 bladrosetter under klen senvuxen gran.</t>
+          <t>I blom och fler rosetter på fler fläckar.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7024,13 +7005,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122817980</t>
+          <t>https://artportalen.se/Sighting/118680966</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122821104</v>
+        <v>122817980</v>
       </c>
       <c r="B54" t="n">
         <v>99118</v>
@@ -7060,12 +7041,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -7080,14 +7061,14 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>524057</v>
+        <v>524038</v>
       </c>
       <c r="R54" t="n">
-        <v>6714094</v>
+        <v>6713288</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7119,7 +7100,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7129,12 +7110,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
+          <t>10-15 bladrosetter under klen senvuxen gran.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7160,13 +7141,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122821104</t>
+          <t>https://artportalen.se/Sighting/122817980</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122821198</v>
+        <v>122821104</v>
       </c>
       <c r="B55" t="n">
         <v>99118</v>
@@ -7196,12 +7177,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -7209,7 +7190,6 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -7221,10 +7201,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>524049</v>
+        <v>524057</v>
       </c>
       <c r="R55" t="n">
-        <v>6714097</v>
+        <v>6714094</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7236,7 +7216,7 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>Falun</t>
+          <t>Borlänge</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -7271,7 +7251,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Under klen gran. En överblommad.</t>
+          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7280,7 +7260,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7298,13 +7277,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122821198</t>
+          <t>https://artportalen.se/Sighting/122821104</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122821729</v>
+        <v>122821198</v>
       </c>
       <c r="B56" t="n">
         <v>99118</v>
@@ -7334,12 +7313,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -7347,6 +7326,7 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -7358,10 +7338,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>524077</v>
+        <v>524049</v>
       </c>
       <c r="R56" t="n">
-        <v>6714076</v>
+        <v>6714097</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7373,7 +7353,7 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>Borlänge</t>
+          <t>Falun</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -7393,7 +7373,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7403,12 +7383,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>Under klen gran. En överblommad.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7417,6 +7397,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7434,13 +7415,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122821729</t>
+          <t>https://artportalen.se/Sighting/122821198</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122821745</v>
+        <v>122821729</v>
       </c>
       <c r="B57" t="n">
         <v>99118</v>
@@ -7470,7 +7451,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7494,10 +7475,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>524080</v>
+        <v>524077</v>
       </c>
       <c r="R57" t="n">
-        <v>6714074</v>
+        <v>6714076</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7529,7 +7510,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7539,7 +7520,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7565,13 +7551,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122821745</t>
+          <t>https://artportalen.se/Sighting/122821729</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122821824</v>
+        <v>122821745</v>
       </c>
       <c r="B58" t="n">
         <v>99118</v>
@@ -7606,7 +7592,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -7625,10 +7611,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>524055</v>
+        <v>524080</v>
       </c>
       <c r="R58" t="n">
-        <v>6714048</v>
+        <v>6714074</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7660,7 +7646,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7670,7 +7656,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7696,13 +7682,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122821824</t>
+          <t>https://artportalen.se/Sighting/122821745</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122916997</v>
+        <v>122821824</v>
       </c>
       <c r="B59" t="n">
         <v>99118</v>
@@ -7732,12 +7718,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -7752,14 +7738,14 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>524142</v>
+        <v>524055</v>
       </c>
       <c r="R59" t="n">
-        <v>6713729</v>
+        <v>6714048</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7786,27 +7772,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>17:33</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7832,13 +7813,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122916997</t>
+          <t>https://artportalen.se/Sighting/122821824</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122917069</v>
+        <v>122916997</v>
       </c>
       <c r="B60" t="n">
         <v>99118</v>
@@ -7868,12 +7849,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -7892,7 +7873,7 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>524154</v>
+        <v>524142</v>
       </c>
       <c r="R60" t="n">
         <v>6713729</v>
@@ -7927,7 +7908,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7937,12 +7918,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>En överblommad.</t>
+          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7968,13 +7949,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122917069</t>
+          <t>https://artportalen.se/Sighting/122916997</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122957710</v>
+        <v>122917069</v>
       </c>
       <c r="B61" t="n">
         <v>99118</v>
@@ -8004,7 +7985,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -8017,16 +7998,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>524145</v>
+        <v>524154</v>
       </c>
       <c r="R61" t="n">
-        <v>6713733</v>
+        <v>6713729</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8053,27 +8039,27 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Under klena granar.</t>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8099,13 +8085,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122957710</t>
+          <t>https://artportalen.se/Sighting/122917069</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122958064</v>
+        <v>122957710</v>
       </c>
       <c r="B62" t="n">
         <v>99118</v>
@@ -8135,12 +8121,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -8148,21 +8134,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>524144</v>
+        <v>524145</v>
       </c>
       <c r="R62" t="n">
-        <v>6713722</v>
+        <v>6713733</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8194,7 +8175,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8204,12 +8185,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
+          <t>Under klena granar.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8235,13 +8216,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122958064</t>
+          <t>https://artportalen.se/Sighting/122957710</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122958244</v>
+        <v>122958064</v>
       </c>
       <c r="B63" t="n">
         <v>99118</v>
@@ -8271,12 +8252,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -8295,10 +8276,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>524143</v>
+        <v>524144</v>
       </c>
       <c r="R63" t="n">
-        <v>6713721</v>
+        <v>6713722</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8330,7 +8311,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8340,12 +8321,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ca 20 bladrosetter. Kanske fler.</t>
+          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8371,13 +8352,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122958244</t>
+          <t>https://artportalen.se/Sighting/122958064</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122958484</v>
+        <v>122958244</v>
       </c>
       <c r="B64" t="n">
         <v>99118</v>
@@ -8407,7 +8388,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -8431,10 +8412,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>524142</v>
+        <v>524143</v>
       </c>
       <c r="R64" t="n">
-        <v>6713723</v>
+        <v>6713721</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8466,7 +8447,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8476,7 +8457,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter. Kanske fler.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8502,13 +8488,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122958484</t>
+          <t>https://artportalen.se/Sighting/122958244</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122958550</v>
+        <v>122958484</v>
       </c>
       <c r="B65" t="n">
         <v>99118</v>
@@ -8538,7 +8524,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8562,10 +8548,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>524147</v>
+        <v>524142</v>
       </c>
       <c r="R65" t="n">
-        <v>6713728</v>
+        <v>6713723</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8597,7 +8583,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8607,12 +8593,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8638,13 +8619,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122958550</t>
+          <t>https://artportalen.se/Sighting/122958484</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122958631</v>
+        <v>122958550</v>
       </c>
       <c r="B66" t="n">
         <v>99118</v>
@@ -8674,7 +8655,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -8698,10 +8679,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>524136</v>
+        <v>524147</v>
       </c>
       <c r="R66" t="n">
-        <v>6713723</v>
+        <v>6713728</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8733,7 +8714,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8743,12 +8724,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Bladrosetter och en överblommad.</t>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8774,13 +8755,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122958631</t>
+          <t>https://artportalen.se/Sighting/122958550</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122959503</v>
+        <v>122958631</v>
       </c>
       <c r="B67" t="n">
         <v>99118</v>
@@ -8810,12 +8791,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -8823,16 +8804,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>524145</v>
+        <v>524136</v>
       </c>
       <c r="R67" t="n">
-        <v>6713672</v>
+        <v>6713723</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8864,7 +8850,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8874,7 +8860,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Bladrosetter och en överblommad.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8900,13 +8891,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122959503</t>
+          <t>https://artportalen.se/Sighting/122958631</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123412257</v>
+        <v>122959503</v>
       </c>
       <c r="B68" t="n">
         <v>99118</v>
@@ -8936,7 +8927,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8951,14 +8942,14 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>524123</v>
+        <v>524145</v>
       </c>
       <c r="R68" t="n">
-        <v>6713637</v>
+        <v>6713672</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8985,22 +8976,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9026,13 +9017,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123412257</t>
+          <t>https://artportalen.se/Sighting/122959503</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123412326</v>
+        <v>123412257</v>
       </c>
       <c r="B69" t="n">
         <v>99118</v>
@@ -9062,7 +9053,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9081,10 +9072,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>524122</v>
+        <v>524123</v>
       </c>
       <c r="R69" t="n">
-        <v>6713640</v>
+        <v>6713637</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9116,7 +9107,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9126,7 +9117,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9152,13 +9143,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123412326</t>
+          <t>https://artportalen.se/Sighting/123412257</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123412367</v>
+        <v>123412326</v>
       </c>
       <c r="B70" t="n">
         <v>99118</v>
@@ -9188,7 +9179,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9203,14 +9194,14 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>524136</v>
+        <v>524122</v>
       </c>
       <c r="R70" t="n">
-        <v>6713648</v>
+        <v>6713640</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9242,7 +9233,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9252,7 +9243,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9278,13 +9269,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123412367</t>
+          <t>https://artportalen.se/Sighting/123412326</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123412439</v>
+        <v>123412367</v>
       </c>
       <c r="B71" t="n">
         <v>99118</v>
@@ -9314,7 +9305,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9327,21 +9318,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>524137</v>
+        <v>524136</v>
       </c>
       <c r="R71" t="n">
-        <v>6713646</v>
+        <v>6713648</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9373,7 +9359,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9383,12 +9369,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:39</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Inom ca 5 kv/dm.</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9414,13 +9395,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123412439</t>
+          <t>https://artportalen.se/Sighting/123412367</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123412973</v>
+        <v>123412439</v>
       </c>
       <c r="B72" t="n">
         <v>99118</v>
@@ -9450,7 +9431,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9474,10 +9455,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>524116</v>
+        <v>524137</v>
       </c>
       <c r="R72" t="n">
-        <v>6713634</v>
+        <v>6713646</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9509,7 +9490,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9519,7 +9500,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Inom ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9545,13 +9531,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123412973</t>
+          <t>https://artportalen.se/Sighting/123412439</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123413078</v>
+        <v>123412973</v>
       </c>
       <c r="B73" t="n">
         <v>99118</v>
@@ -9581,7 +9567,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9601,14 +9587,14 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>524102</v>
+        <v>524116</v>
       </c>
       <c r="R73" t="n">
-        <v>6713632</v>
+        <v>6713634</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9640,7 +9626,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9650,7 +9636,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9676,13 +9662,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123413078</t>
+          <t>https://artportalen.se/Sighting/123412973</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123413119</v>
+        <v>123413078</v>
       </c>
       <c r="B74" t="n">
         <v>99118</v>
@@ -9712,12 +9698,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -9725,7 +9711,6 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -9737,10 +9722,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>524101</v>
+        <v>524102</v>
       </c>
       <c r="R74" t="n">
-        <v>6713638</v>
+        <v>6713632</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9772,7 +9757,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9782,12 +9767,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>17:59</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Spridda sporadiskt över ytan.</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9796,7 +9776,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -9814,13 +9793,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123413119</t>
+          <t>https://artportalen.se/Sighting/123413078</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123413726</v>
+        <v>123413119</v>
       </c>
       <c r="B75" t="n">
         <v>99118</v>
@@ -9855,7 +9834,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -9863,16 +9842,22 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>524030</v>
+        <v>524101</v>
       </c>
       <c r="R75" t="n">
-        <v>6713469</v>
+        <v>6713638</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9904,7 +9889,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9914,7 +9899,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Spridda sporadiskt över ytan.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9923,6 +9913,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -9940,13 +9931,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123413726</t>
+          <t>https://artportalen.se/Sighting/123413119</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123413856</v>
+        <v>123413726</v>
       </c>
       <c r="B76" t="n">
         <v>99118</v>
@@ -9976,7 +9967,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9995,10 +9986,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>524041</v>
+        <v>524030</v>
       </c>
       <c r="R76" t="n">
-        <v>6713443</v>
+        <v>6713469</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10030,7 +10021,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10040,7 +10031,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10066,13 +10057,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123413856</t>
+          <t>https://artportalen.se/Sighting/123413726</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123414270</v>
+        <v>123413856</v>
       </c>
       <c r="B77" t="n">
         <v>99118</v>
@@ -10102,7 +10093,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -10121,10 +10112,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>524085</v>
+        <v>524041</v>
       </c>
       <c r="R77" t="n">
-        <v>6713390</v>
+        <v>6713443</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10156,7 +10147,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10166,7 +10157,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10192,13 +10183,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123414270</t>
+          <t>https://artportalen.se/Sighting/123413856</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123414352</v>
+        <v>123414270</v>
       </c>
       <c r="B78" t="n">
         <v>99118</v>
@@ -10228,7 +10219,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -10247,10 +10238,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>524098</v>
+        <v>524085</v>
       </c>
       <c r="R78" t="n">
-        <v>6713405</v>
+        <v>6713390</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10282,7 +10273,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10292,7 +10283,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10318,13 +10309,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123414352</t>
+          <t>https://artportalen.se/Sighting/123414270</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123525488</v>
+        <v>123414352</v>
       </c>
       <c r="B79" t="n">
         <v>99118</v>
@@ -10359,7 +10350,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -10367,21 +10358,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>524128</v>
+        <v>524098</v>
       </c>
       <c r="R79" t="n">
-        <v>6714020</v>
+        <v>6713405</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10408,27 +10394,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>16:22</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>En överblommad.</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10454,13 +10435,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123525488</t>
+          <t>https://artportalen.se/Sighting/123414352</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123526406</v>
+        <v>123525488</v>
       </c>
       <c r="B80" t="n">
         <v>99118</v>
@@ -10490,7 +10471,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -10514,10 +10495,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>524109</v>
+        <v>524128</v>
       </c>
       <c r="R80" t="n">
-        <v>6713892</v>
+        <v>6714020</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10549,7 +10530,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10559,12 +10540,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>2 fläckar med ca 10-15 bladrosetter på varje ställe.</t>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10590,13 +10571,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123526406</t>
+          <t>https://artportalen.se/Sighting/123525488</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123526470</v>
+        <v>123526406</v>
       </c>
       <c r="B81" t="n">
         <v>99118</v>
@@ -10626,12 +10607,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -10650,10 +10631,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>524101</v>
+        <v>524109</v>
       </c>
       <c r="R81" t="n">
-        <v>6713880</v>
+        <v>6713892</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10685,7 +10666,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10695,7 +10676,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>2 fläckar med ca 10-15 bladrosetter på varje ställe.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10721,13 +10707,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123526470</t>
+          <t>https://artportalen.se/Sighting/123526406</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>123527655</v>
+        <v>123526470</v>
       </c>
       <c r="B82" t="n">
         <v>99118</v>
@@ -10757,7 +10743,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10770,16 +10756,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>524041</v>
+        <v>524101</v>
       </c>
       <c r="R82" t="n">
-        <v>6713460</v>
+        <v>6713880</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10811,7 +10802,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10821,7 +10812,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10847,13 +10838,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123527655</t>
+          <t>https://artportalen.se/Sighting/123526470</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123527741</v>
+        <v>123527655</v>
       </c>
       <c r="B83" t="n">
         <v>99118</v>
@@ -10883,12 +10874,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -10896,18 +10887,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>524029</v>
+        <v>524041</v>
       </c>
       <c r="R83" t="n">
-        <v>6713459</v>
+        <v>6713460</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10939,7 +10928,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10949,12 +10938,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Sporadiskt spridda över ytan.</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10963,7 +10947,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -10981,13 +10964,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123527741</t>
+          <t>https://artportalen.se/Sighting/123527655</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123528345</v>
+        <v>123527741</v>
       </c>
       <c r="B84" t="n">
         <v>99118</v>
@@ -11017,7 +11000,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -11038,10 +11021,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>524025</v>
+        <v>524029</v>
       </c>
       <c r="R84" t="n">
-        <v>6713476</v>
+        <v>6713459</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11073,7 +11056,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11083,12 +11066,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>En överblommad.</t>
+          <t>Sporadiskt spridda över ytan.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11115,13 +11098,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123528345</t>
+          <t>https://artportalen.se/Sighting/123527741</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>123564666</v>
+        <v>123528345</v>
       </c>
       <c r="B85" t="n">
         <v>99118</v>
@@ -11151,12 +11134,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -11164,16 +11147,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>524034</v>
+        <v>524025</v>
       </c>
       <c r="R85" t="n">
-        <v>6713303</v>
+        <v>6713476</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11200,22 +11185,27 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11224,6 +11214,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -11241,13 +11232,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123564666</t>
+          <t>https://artportalen.se/Sighting/123528345</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>123564906</v>
+        <v>123564666</v>
       </c>
       <c r="B86" t="n">
         <v>99118</v>
@@ -11277,7 +11268,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -11296,10 +11287,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>524050</v>
+        <v>524034</v>
       </c>
       <c r="R86" t="n">
-        <v>6713310</v>
+        <v>6713303</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11331,7 +11322,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11341,7 +11332,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11367,13 +11358,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123564906</t>
+          <t>https://artportalen.se/Sighting/123564666</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>123566656</v>
+        <v>123564906</v>
       </c>
       <c r="B87" t="n">
         <v>99118</v>
@@ -11403,7 +11394,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -11422,10 +11413,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>524082</v>
+        <v>524050</v>
       </c>
       <c r="R87" t="n">
-        <v>6713393</v>
+        <v>6713310</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11457,7 +11448,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11467,7 +11458,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11493,13 +11484,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123566656</t>
+          <t>https://artportalen.se/Sighting/123564906</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>123566767</v>
+        <v>123566656</v>
       </c>
       <c r="B88" t="n">
         <v>99118</v>
@@ -11529,7 +11520,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -11548,10 +11539,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524084</v>
+        <v>524082</v>
       </c>
       <c r="R88" t="n">
-        <v>6713408</v>
+        <v>6713393</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11583,7 +11574,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11593,7 +11584,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11619,13 +11610,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123566767</t>
+          <t>https://artportalen.se/Sighting/123566656</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>123567299</v>
+        <v>123566767</v>
       </c>
       <c r="B89" t="n">
         <v>99118</v>
@@ -11655,7 +11646,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -11674,10 +11665,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>524117</v>
+        <v>524084</v>
       </c>
       <c r="R89" t="n">
-        <v>6713411</v>
+        <v>6713408</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11709,7 +11700,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11719,7 +11710,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11745,13 +11736,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123567299</t>
+          <t>https://artportalen.se/Sighting/123566767</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>123567823</v>
+        <v>123567299</v>
       </c>
       <c r="B90" t="n">
         <v>99118</v>
@@ -11781,7 +11772,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -11800,10 +11791,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>524093</v>
+        <v>524117</v>
       </c>
       <c r="R90" t="n">
-        <v>6713439</v>
+        <v>6713411</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11835,7 +11826,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11845,7 +11836,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11871,13 +11862,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123567823</t>
+          <t>https://artportalen.se/Sighting/123567299</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>123570699</v>
+        <v>123567823</v>
       </c>
       <c r="B91" t="n">
         <v>99118</v>
@@ -11907,7 +11898,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -11926,10 +11917,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>524145</v>
+        <v>524093</v>
       </c>
       <c r="R91" t="n">
-        <v>6713399</v>
+        <v>6713439</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11961,7 +11952,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11971,7 +11962,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11997,13 +11988,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123570699</t>
+          <t>https://artportalen.se/Sighting/123567823</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>123760786</v>
+        <v>123570699</v>
       </c>
       <c r="B92" t="n">
         <v>99118</v>
@@ -12033,7 +12024,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -12048,14 +12039,14 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>523969</v>
+        <v>524145</v>
       </c>
       <c r="R92" t="n">
-        <v>6713750</v>
+        <v>6713399</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -12082,22 +12073,22 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -12123,13 +12114,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123760786</t>
+          <t>https://artportalen.se/Sighting/123570699</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>123761091</v>
+        <v>123760786</v>
       </c>
       <c r="B93" t="n">
         <v>99118</v>
@@ -12159,7 +12150,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -12178,10 +12169,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>523962</v>
+        <v>523969</v>
       </c>
       <c r="R93" t="n">
-        <v>6713819</v>
+        <v>6713750</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -12213,7 +12204,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -12223,7 +12214,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -12249,13 +12240,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123761091</t>
+          <t>https://artportalen.se/Sighting/123760786</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124431501</v>
+        <v>123761091</v>
       </c>
       <c r="B94" t="n">
         <v>99118</v>
@@ -12285,7 +12276,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -12300,14 +12291,14 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>524175</v>
+        <v>523962</v>
       </c>
       <c r="R94" t="n">
-        <v>6713573</v>
+        <v>6713819</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -12334,27 +12325,22 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>18:08</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Under senvuxen klen gran.</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -12380,13 +12366,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124431501</t>
+          <t>https://artportalen.se/Sighting/123761091</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124431841</v>
+        <v>124431501</v>
       </c>
       <c r="B95" t="n">
         <v>99118</v>
@@ -12416,7 +12402,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -12435,10 +12421,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>524168</v>
+        <v>524175</v>
       </c>
       <c r="R95" t="n">
-        <v>6713526</v>
+        <v>6713573</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12470,7 +12456,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12480,7 +12466,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Under senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12506,13 +12497,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124431841</t>
+          <t>https://artportalen.se/Sighting/124431501</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124432135</v>
+        <v>124431841</v>
       </c>
       <c r="B96" t="n">
         <v>99118</v>
@@ -12542,7 +12533,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -12561,10 +12552,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>524180</v>
+        <v>524168</v>
       </c>
       <c r="R96" t="n">
-        <v>6713485</v>
+        <v>6713526</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12596,7 +12587,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12606,7 +12597,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12632,13 +12623,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124432135</t>
+          <t>https://artportalen.se/Sighting/124431841</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124432412</v>
+        <v>124432135</v>
       </c>
       <c r="B97" t="n">
         <v>99118</v>
@@ -12668,7 +12659,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -12687,10 +12678,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>524183</v>
+        <v>524180</v>
       </c>
       <c r="R97" t="n">
-        <v>6713449</v>
+        <v>6713485</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12722,7 +12713,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12732,7 +12723,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12758,13 +12749,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124432412</t>
+          <t>https://artportalen.se/Sighting/124432135</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124433963</v>
+        <v>124432412</v>
       </c>
       <c r="B98" t="n">
         <v>99118</v>
@@ -12794,7 +12785,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -12813,10 +12804,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>524033</v>
+        <v>524183</v>
       </c>
       <c r="R98" t="n">
-        <v>6713451</v>
+        <v>6713449</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12848,7 +12839,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12858,7 +12849,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12884,13 +12875,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124433963</t>
+          <t>https://artportalen.se/Sighting/124432412</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124434100</v>
+        <v>124433963</v>
       </c>
       <c r="B99" t="n">
         <v>99118</v>
@@ -12920,7 +12911,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -12933,21 +12924,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>524042</v>
+        <v>524033</v>
       </c>
       <c r="R99" t="n">
-        <v>6713423</v>
+        <v>6713451</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12979,7 +12965,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12989,12 +12975,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Över ca 5 kv/dm.</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13020,13 +13001,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124434100</t>
+          <t>https://artportalen.se/Sighting/124433963</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124435133</v>
+        <v>124434100</v>
       </c>
       <c r="B100" t="n">
         <v>99118</v>
@@ -13056,7 +13037,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -13076,14 +13057,14 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>523934</v>
+        <v>524042</v>
       </c>
       <c r="R100" t="n">
-        <v>6713790</v>
+        <v>6713423</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13115,7 +13096,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -13125,12 +13106,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>En vinterståndare.</t>
+          <t>Över ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13156,13 +13137,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124435133</t>
+          <t>https://artportalen.se/Sighting/124434100</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124711417</v>
+        <v>124435133</v>
       </c>
       <c r="B101" t="n">
         <v>99118</v>
@@ -13192,7 +13173,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -13205,16 +13186,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>524045</v>
+        <v>523934</v>
       </c>
       <c r="R101" t="n">
-        <v>6713421</v>
+        <v>6713790</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13241,22 +13227,27 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>En vinterståndare.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13282,13 +13273,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124711417</t>
+          <t>https://artportalen.se/Sighting/124435133</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125899247</v>
+        <v>124711417</v>
       </c>
       <c r="B102" t="n">
         <v>99118</v>
@@ -13318,7 +13309,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -13337,10 +13328,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>524042</v>
+        <v>524045</v>
       </c>
       <c r="R102" t="n">
-        <v>6713304</v>
+        <v>6713421</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13367,22 +13358,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13408,13 +13399,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125899247</t>
+          <t>https://artportalen.se/Sighting/124711417</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126932450</v>
+        <v>125899247</v>
       </c>
       <c r="B103" t="n">
         <v>99118</v>
@@ -13444,29 +13435,29 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>524097</v>
+        <v>524042</v>
       </c>
       <c r="R103" t="n">
-        <v>6713893</v>
+        <v>6713304</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13493,22 +13484,22 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13534,13 +13525,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126932450</t>
+          <t>https://artportalen.se/Sighting/125899247</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126932846</v>
+        <v>126932450</v>
       </c>
       <c r="B104" t="n">
         <v>99118</v>
@@ -13570,7 +13561,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -13585,14 +13576,14 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>524149</v>
+        <v>524097</v>
       </c>
       <c r="R104" t="n">
-        <v>6713719</v>
+        <v>6713893</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13624,7 +13615,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13634,7 +13625,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13660,13 +13651,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126932846</t>
+          <t>https://artportalen.se/Sighting/126932450</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126933275</v>
+        <v>126932846</v>
       </c>
       <c r="B105" t="n">
         <v>99118</v>
@@ -13696,7 +13687,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -13711,14 +13702,14 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>524034</v>
+        <v>524149</v>
       </c>
       <c r="R105" t="n">
-        <v>6713423</v>
+        <v>6713719</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -13750,7 +13741,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13760,7 +13751,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13786,13 +13777,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126933275</t>
+          <t>https://artportalen.se/Sighting/126932846</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126933326</v>
+        <v>126933275</v>
       </c>
       <c r="B106" t="n">
         <v>99118</v>
@@ -13841,10 +13832,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>524053</v>
+        <v>524034</v>
       </c>
       <c r="R106" t="n">
-        <v>6713414</v>
+        <v>6713423</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -13876,7 +13867,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -13886,7 +13877,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13912,13 +13903,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126933326</t>
+          <t>https://artportalen.se/Sighting/126933275</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126933611</v>
+        <v>126933326</v>
       </c>
       <c r="B107" t="n">
         <v>99118</v>
@@ -13967,10 +13958,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>524037</v>
+        <v>524053</v>
       </c>
       <c r="R107" t="n">
-        <v>6713298</v>
+        <v>6713414</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -14002,7 +13993,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -14012,7 +14003,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -14038,13 +14029,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126933611</t>
+          <t>https://artportalen.se/Sighting/126933326</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126933692</v>
+        <v>126933611</v>
       </c>
       <c r="B108" t="n">
         <v>99118</v>
@@ -14093,10 +14084,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>524033</v>
+        <v>524037</v>
       </c>
       <c r="R108" t="n">
-        <v>6713299</v>
+        <v>6713298</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -14164,13 +14155,13 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126933692</t>
+          <t>https://artportalen.se/Sighting/126933611</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126934164</v>
+        <v>126933692</v>
       </c>
       <c r="B109" t="n">
         <v>99118</v>
@@ -14200,7 +14191,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -14219,10 +14210,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>524047</v>
+        <v>524033</v>
       </c>
       <c r="R109" t="n">
-        <v>6713301</v>
+        <v>6713299</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -14254,7 +14245,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -14264,7 +14255,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -14290,13 +14281,13 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126934164</t>
+          <t>https://artportalen.se/Sighting/126933692</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126934577</v>
+        <v>126934164</v>
       </c>
       <c r="B110" t="n">
         <v>99118</v>
@@ -14326,7 +14317,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -14345,10 +14336,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>524036</v>
+        <v>524047</v>
       </c>
       <c r="R110" t="n">
-        <v>6713293</v>
+        <v>6713301</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -14380,7 +14371,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -14390,7 +14381,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -14416,13 +14407,13 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126934577</t>
+          <t>https://artportalen.se/Sighting/126934164</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126934586</v>
+        <v>126934577</v>
       </c>
       <c r="B111" t="n">
         <v>99118</v>
@@ -14452,7 +14443,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -14465,18 +14456,16 @@
           <t>blomning</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>524034</v>
+        <v>524036</v>
       </c>
       <c r="R111" t="n">
-        <v>6713294</v>
+        <v>6713293</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -14508,7 +14497,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -14518,7 +14507,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -14527,7 +14516,6 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -14545,13 +14533,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126934586</t>
+          <t>https://artportalen.se/Sighting/126934577</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126934603</v>
+        <v>126934586</v>
       </c>
       <c r="B112" t="n">
         <v>99118</v>
@@ -14581,7 +14569,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -14594,6 +14582,8 @@
           <t>blomning</t>
         </is>
       </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
@@ -14603,7 +14593,7 @@
         <v>524034</v>
       </c>
       <c r="R112" t="n">
-        <v>6713296</v>
+        <v>6713294</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -14635,7 +14625,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -14645,7 +14635,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -14654,6 +14644,7 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
@@ -14671,13 +14662,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126934603</t>
+          <t>https://artportalen.se/Sighting/126934586</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126935325</v>
+        <v>126934603</v>
       </c>
       <c r="B113" t="n">
         <v>99118</v>
@@ -14726,10 +14717,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>524091</v>
+        <v>524034</v>
       </c>
       <c r="R113" t="n">
-        <v>6713327</v>
+        <v>6713296</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14761,7 +14752,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -14771,7 +14762,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -14797,13 +14788,13 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126935325</t>
+          <t>https://artportalen.se/Sighting/126934603</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126936299</v>
+        <v>126935325</v>
       </c>
       <c r="B114" t="n">
         <v>99118</v>
@@ -14833,7 +14824,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -14852,10 +14843,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>524172</v>
+        <v>524091</v>
       </c>
       <c r="R114" t="n">
-        <v>6713431</v>
+        <v>6713327</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -14887,7 +14878,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -14897,7 +14888,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14923,13 +14914,13 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126936299</t>
+          <t>https://artportalen.se/Sighting/126935325</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126936539</v>
+        <v>126936299</v>
       </c>
       <c r="B115" t="n">
         <v>99118</v>
@@ -14978,10 +14969,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>524155</v>
+        <v>524172</v>
       </c>
       <c r="R115" t="n">
-        <v>6713596</v>
+        <v>6713431</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -15013,7 +15004,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -15023,7 +15014,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -15049,13 +15040,13 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126936539</t>
+          <t>https://artportalen.se/Sighting/126936299</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126961591</v>
+        <v>126936539</v>
       </c>
       <c r="B116" t="n">
         <v>99118</v>
@@ -15085,12 +15076,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -15100,14 +15091,14 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>524075</v>
+        <v>524155</v>
       </c>
       <c r="R116" t="n">
-        <v>6714105</v>
+        <v>6713596</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -15134,27 +15125,22 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>17:39</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>8 I blom över ytan, rikligt med bladrosetter också.</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -15180,13 +15166,13 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126961591</t>
+          <t>https://artportalen.se/Sighting/126936539</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126962144</v>
+        <v>126961591</v>
       </c>
       <c r="B117" t="n">
         <v>99118</v>
@@ -15216,12 +15202,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -15235,10 +15221,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>524099</v>
+        <v>524075</v>
       </c>
       <c r="R117" t="n">
-        <v>6713924</v>
+        <v>6714105</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -15270,7 +15256,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -15280,7 +15266,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>8 I blom över ytan, rikligt med bladrosetter också.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -15306,13 +15297,13 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126962144</t>
+          <t>https://artportalen.se/Sighting/126961591</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126962269</v>
+        <v>126962144</v>
       </c>
       <c r="B118" t="n">
         <v>99118</v>
@@ -15361,10 +15352,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>524049</v>
+        <v>524099</v>
       </c>
       <c r="R118" t="n">
-        <v>6713929</v>
+        <v>6713924</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -15396,7 +15387,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -15406,7 +15397,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -15432,13 +15423,13 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126962269</t>
+          <t>https://artportalen.se/Sighting/126962144</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126962421</v>
+        <v>126962269</v>
       </c>
       <c r="B119" t="n">
         <v>99118</v>
@@ -15468,7 +15459,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -15483,14 +15474,14 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>524038</v>
+        <v>524049</v>
       </c>
       <c r="R119" t="n">
-        <v>6713919</v>
+        <v>6713929</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -15522,7 +15513,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -15532,7 +15523,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15558,13 +15549,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126962421</t>
+          <t>https://artportalen.se/Sighting/126962269</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126962844</v>
+        <v>126962421</v>
       </c>
       <c r="B120" t="n">
         <v>99118</v>
@@ -15594,7 +15585,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -15609,14 +15600,14 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524143</v>
+        <v>524038</v>
       </c>
       <c r="R120" t="n">
-        <v>6713665</v>
+        <v>6713919</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15648,7 +15639,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15658,7 +15649,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15684,13 +15675,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126962844</t>
+          <t>https://artportalen.se/Sighting/126962421</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126963368</v>
+        <v>126962844</v>
       </c>
       <c r="B121" t="n">
         <v>99118</v>
@@ -15735,14 +15726,14 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>524091</v>
+        <v>524143</v>
       </c>
       <c r="R121" t="n">
-        <v>6713407</v>
+        <v>6713665</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15774,7 +15765,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15784,7 +15775,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15810,13 +15801,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126963368</t>
+          <t>https://artportalen.se/Sighting/126962844</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126963427</v>
+        <v>126963368</v>
       </c>
       <c r="B122" t="n">
         <v>99118</v>
@@ -15865,10 +15856,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>524088</v>
+        <v>524091</v>
       </c>
       <c r="R122" t="n">
-        <v>6713405</v>
+        <v>6713407</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15900,7 +15891,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15910,7 +15901,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15936,13 +15927,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126963427</t>
+          <t>https://artportalen.se/Sighting/126963368</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126963583</v>
+        <v>126963427</v>
       </c>
       <c r="B123" t="n">
         <v>99118</v>
@@ -15972,7 +15963,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -15985,21 +15976,16 @@
           <t>blomning</t>
         </is>
       </c>
-      <c r="N123" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>524077</v>
+        <v>524088</v>
       </c>
       <c r="R123" t="n">
-        <v>6713430</v>
+        <v>6713405</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -16031,7 +16017,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -16041,12 +16027,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>19:05</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Över yta på ca 5 kv/m</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -16072,13 +16053,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126963583</t>
+          <t>https://artportalen.se/Sighting/126963427</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127727170</v>
+        <v>126963583</v>
       </c>
       <c r="B124" t="n">
         <v>99118</v>
@@ -16108,7 +16089,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -16116,16 +16097,26 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>524154</v>
+        <v>524077</v>
       </c>
       <c r="R124" t="n">
-        <v>6713653</v>
+        <v>6713430</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -16152,22 +16143,27 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Över yta på ca 5 kv/m</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -16193,13 +16189,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127727170</t>
+          <t>https://artportalen.se/Sighting/126963583</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127727173</v>
+        <v>127727170</v>
       </c>
       <c r="B125" t="n">
         <v>99118</v>
@@ -16229,7 +16225,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -16246,7 +16242,7 @@
         <v>524154</v>
       </c>
       <c r="R125" t="n">
-        <v>6713656</v>
+        <v>6713653</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -16314,13 +16310,13 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127727173</t>
+          <t>https://artportalen.se/Sighting/127727170</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129064197</v>
+        <v>127727173</v>
       </c>
       <c r="B126" t="n">
         <v>99118</v>
@@ -16355,24 +16351,19 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>524099</v>
+        <v>524154</v>
       </c>
       <c r="R126" t="n">
-        <v>6714137</v>
+        <v>6713656</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -16384,7 +16375,7 @@
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>Falun</t>
+          <t>Borlänge</t>
         </is>
       </c>
       <c r="V126" t="inlineStr">
@@ -16394,27 +16385,27 @@
       </c>
       <c r="W126" t="inlineStr">
         <is>
-          <t>Aspeboda</t>
+          <t>Borlänge</t>
         </is>
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -16440,13 +16431,13 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129064197</t>
+          <t>https://artportalen.se/Sighting/127727173</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129064260</v>
+        <v>129064197</v>
       </c>
       <c r="B127" t="n">
         <v>99118</v>
@@ -16474,7 +16465,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K127" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -16486,10 +16486,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>524107</v>
+        <v>524099</v>
       </c>
       <c r="R127" t="n">
-        <v>6714128</v>
+        <v>6714137</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -16521,7 +16521,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -16531,7 +16531,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -16557,13 +16557,13 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129064260</t>
+          <t>https://artportalen.se/Sighting/129064197</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129114973</v>
+        <v>129064260</v>
       </c>
       <c r="B128" t="n">
         <v>99118</v>
@@ -16591,34 +16591,25 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>524137</v>
+        <v>524107</v>
       </c>
       <c r="R128" t="n">
-        <v>6713729</v>
+        <v>6714128</v>
       </c>
       <c r="S128" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -16627,7 +16618,7 @@
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>Borlänge</t>
+          <t>Falun</t>
         </is>
       </c>
       <c r="V128" t="inlineStr">
@@ -16637,27 +16628,27 @@
       </c>
       <c r="W128" t="inlineStr">
         <is>
-          <t>Borlänge</t>
+          <t>Aspeboda</t>
         </is>
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -16683,13 +16674,13 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129114973</t>
+          <t>https://artportalen.se/Sighting/129064260</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129115572</v>
+        <v>129114973</v>
       </c>
       <c r="B129" t="n">
         <v>99118</v>
@@ -16719,32 +16710,32 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>524075</v>
+        <v>524137</v>
       </c>
       <c r="R129" t="n">
-        <v>6713417</v>
+        <v>6713729</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -16773,7 +16764,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -16783,7 +16774,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -16809,44 +16800,53 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129115572</t>
+          <t>https://artportalen.se/Sighting/129114973</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>123569808</v>
+        <v>129115572</v>
       </c>
       <c r="B130" t="n">
-        <v>97983</v>
+        <v>99118</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="N130" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -16855,10 +16855,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>524077</v>
+        <v>524075</v>
       </c>
       <c r="R130" t="n">
-        <v>6713436</v>
+        <v>6713417</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -16885,22 +16885,22 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-03-29</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -16926,16 +16926,16 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123569808</t>
+          <t>https://artportalen.se/Sighting/129115572</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>123569630</v>
+        <v>123569808</v>
       </c>
       <c r="B131" t="n">
-        <v>101326</v>
+        <v>97983</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16943,35 +16943,24 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L131" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="N131" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -16983,10 +16972,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>524047</v>
+        <v>524077</v>
       </c>
       <c r="R131" t="n">
-        <v>6713427</v>
+        <v>6713436</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -17018,7 +17007,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -17028,12 +17017,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Spridda över ca 15x10m.</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -17042,7 +17026,6 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -17060,13 +17043,13 @@
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123569630</t>
+          <t>https://artportalen.se/Sighting/123569808</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>123762639</v>
+        <v>123569630</v>
       </c>
       <c r="B132" t="n">
         <v>101326</v>
@@ -17096,14 +17079,10 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -17117,14 +17096,14 @@
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>524016</v>
+        <v>524047</v>
       </c>
       <c r="R132" t="n">
-        <v>6713966</v>
+        <v>6713427</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -17151,27 +17130,27 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-03-29</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>På större yta, ca 35x15m, kanske mer. På avverkningsyta där dom dragit basväg rakt över växtplatsen.</t>
+          <t>Spridda över ca 15x10m.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -17198,13 +17177,13 @@
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123762639</t>
+          <t>https://artportalen.se/Sighting/123569630</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>123768932</v>
+        <v>123762639</v>
       </c>
       <c r="B133" t="n">
         <v>101326</v>
@@ -17234,12 +17213,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -17247,16 +17226,22 @@
           <t>blomning</t>
         </is>
       </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>524000</v>
+        <v>524016</v>
       </c>
       <c r="R133" t="n">
-        <v>6713968</v>
+        <v>6713966</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -17283,22 +17268,27 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>20:14</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>På större yta, ca 35x15m, kanske mer. På avverkningsyta där dom dragit basväg rakt över växtplatsen.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -17307,6 +17297,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -17324,13 +17315,13 @@
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123768932</t>
+          <t>https://artportalen.se/Sighting/123762639</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>123768976</v>
+        <v>123768932</v>
       </c>
       <c r="B134" t="n">
         <v>101326</v>
@@ -17358,7 +17349,16 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr"/>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K134" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -17370,10 +17370,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>524011</v>
+        <v>524000</v>
       </c>
       <c r="R134" t="n">
-        <v>6713981</v>
+        <v>6713968</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -17405,7 +17405,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -17415,7 +17415,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -17441,13 +17441,13 @@
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123768976</t>
+          <t>https://artportalen.se/Sighting/123768932</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>123768989</v>
+        <v>123768976</v>
       </c>
       <c r="B135" t="n">
         <v>101326</v>
@@ -17487,10 +17487,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>524017</v>
+        <v>524011</v>
       </c>
       <c r="R135" t="n">
-        <v>6713958</v>
+        <v>6713981</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -17522,7 +17522,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -17532,7 +17532,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -17558,13 +17558,13 @@
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123768989</t>
+          <t>https://artportalen.se/Sighting/123768976</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>123768995</v>
+        <v>123768989</v>
       </c>
       <c r="B136" t="n">
         <v>101326</v>
@@ -17604,10 +17604,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>524011</v>
+        <v>524017</v>
       </c>
       <c r="R136" t="n">
-        <v>6713982</v>
+        <v>6713958</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -17639,7 +17639,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -17649,7 +17649,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -17675,13 +17675,13 @@
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123768995</t>
+          <t>https://artportalen.se/Sighting/123768989</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>123769023</v>
+        <v>123768995</v>
       </c>
       <c r="B137" t="n">
         <v>101326</v>
@@ -17721,10 +17721,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>524017</v>
+        <v>524011</v>
       </c>
       <c r="R137" t="n">
-        <v>6713986</v>
+        <v>6713982</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -17792,13 +17792,13 @@
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123769023</t>
+          <t>https://artportalen.se/Sighting/123768995</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>123769072</v>
+        <v>123769023</v>
       </c>
       <c r="B138" t="n">
         <v>101326</v>
@@ -17826,31 +17826,22 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>524031</v>
+        <v>524017</v>
       </c>
       <c r="R138" t="n">
-        <v>6713998</v>
+        <v>6713986</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -17882,7 +17873,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -17892,7 +17883,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -17918,13 +17909,13 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123769072</t>
+          <t>https://artportalen.se/Sighting/123769023</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>123769093</v>
+        <v>123769072</v>
       </c>
       <c r="B139" t="n">
         <v>101326</v>
@@ -17954,29 +17945,29 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>524033</v>
+        <v>524031</v>
       </c>
       <c r="R139" t="n">
-        <v>6713983</v>
+        <v>6713998</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -18008,7 +17999,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -18018,7 +18009,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -18044,13 +18035,13 @@
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123769093</t>
+          <t>https://artportalen.se/Sighting/123769072</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>123769126</v>
+        <v>123769093</v>
       </c>
       <c r="B140" t="n">
         <v>101326</v>
@@ -18078,7 +18069,16 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr"/>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K140" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -18090,10 +18090,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>524017</v>
+        <v>524033</v>
       </c>
       <c r="R140" t="n">
-        <v>6713977</v>
+        <v>6713983</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -18125,7 +18125,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -18135,7 +18135,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -18161,16 +18161,16 @@
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123769126</t>
+          <t>https://artportalen.se/Sighting/123769093</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>130321255</v>
+        <v>123769126</v>
       </c>
       <c r="B141" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -18195,34 +18195,25 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>524148</v>
+        <v>524017</v>
       </c>
       <c r="R141" t="n">
-        <v>6713407</v>
+        <v>6713977</v>
       </c>
       <c r="S141" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -18246,22 +18237,22 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -18287,16 +18278,16 @@
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130321255</t>
+          <t>https://artportalen.se/Sighting/123769126</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>132755530</v>
+        <v>130321255</v>
       </c>
       <c r="B142" t="n">
-        <v>101403</v>
+        <v>101325</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -18323,29 +18314,29 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>524009</v>
+        <v>524148</v>
       </c>
       <c r="R142" t="n">
-        <v>6714085</v>
+        <v>6713407</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -18357,7 +18348,7 @@
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>Falun</t>
+          <t>Borlänge</t>
         </is>
       </c>
       <c r="V142" t="inlineStr">
@@ -18367,27 +18358,27 @@
       </c>
       <c r="W142" t="inlineStr">
         <is>
-          <t>Aspeboda</t>
+          <t>Borlänge</t>
         </is>
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -18412,6 +18403,132 @@
       </c>
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130321255</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>132755530</v>
+      </c>
+      <c r="B143" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>524009</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6714085</v>
+      </c>
+      <c r="S143" t="n">
+        <v>5</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132755530</t>
         </is>
@@ -18560,6 +18677,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -4998,7 +4998,7 @@
         <v>136991757</v>
       </c>
       <c r="B38" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -4998,7 +4998,7 @@
         <v>136991757</v>
       </c>
       <c r="B38" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -5024,11 +5024,7 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Banvall smedsbo, Smedsbo, Dlr</t>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -4998,7 +4998,7 @@
         <v>136991757</v>
       </c>
       <c r="B38" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -4998,7 +4998,7 @@
         <v>136991757</v>
       </c>
       <c r="B38" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -4998,7 +4998,7 @@
         <v>136991757</v>
       </c>
       <c r="B38" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -4998,7 +4998,7 @@
         <v>136991757</v>
       </c>
       <c r="B38" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
